--- a/server/api/offshore_forecast_api/models/pipeline_feature_importance.xlsx
+++ b/server/api/offshore_forecast_api/models/pipeline_feature_importance.xlsx
@@ -448,14 +448,14 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Water Depth (meter)</t>
+          <t>Panjang (km)</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.3508122265338898</v>
+        <v>0.7225202918052673</v>
       </c>
       <c r="C2" t="n">
-        <v>35.08122253417969</v>
+        <v>72.25202941894531</v>
       </c>
     </row>
     <row r="3">
@@ -465,23 +465,23 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.3480484187602997</v>
+        <v>0.1907675862312317</v>
       </c>
       <c r="C3" t="n">
-        <v>34.80484008789062</v>
+        <v>19.07675933837891</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Panjang (km)</t>
+          <t>Water Depth (meter)</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.3011394143104553</v>
+        <v>0.08671215921640396</v>
       </c>
       <c r="C4" t="n">
-        <v>30.11394119262695</v>
+        <v>8.671216011047363</v>
       </c>
     </row>
   </sheetData>
